--- a/evaluation_surveys/001_financial_governance_confidence_survey--evaluation_surveys.xlsx
+++ b/evaluation_surveys/001_financial_governance_confidence_survey--evaluation_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -803,8 +803,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1121,12 +1121,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1138,12 +1138,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'somewhat_often'}</t>
+          <t>somewhat_often</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Somewhat often'}</t>
+          <t>Somewhat often</t>
         </is>
       </c>
     </row>
@@ -1155,12 +1155,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'often'}</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': 'Often'}</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1172,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_5,_'label':_'almost_always'}</t>
+          <t>almost_always</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 5, 'label': 'Almost always'}</t>
+          <t>Almost always</t>
         </is>
       </c>
     </row>
